--- a/Anylogic_Market/Tables.xlsx
+++ b/Anylogic_Market/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa8ee1148d3b4598/_Main/Assets/Github/Anylogic_Market/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{33434FF7-C561-7F48-8C63-4149471994E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5F52841-8636-F84A-BD40-9268E46C6CD8}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{33434FF7-C561-7F48-8C63-4149471994E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78A0BC68-BDBA-0D4D-8C11-61CB9F9EB651}"/>
   <bookViews>
-    <workbookView xWindow="7760" yWindow="5080" windowWidth="40520" windowHeight="13360" activeTab="1" xr2:uid="{4B8D0DED-1864-DE4D-8EAA-ED31AD29D025}"/>
+    <workbookView xWindow="-20840" yWindow="18840" windowWidth="21340" windowHeight="13180" activeTab="1" xr2:uid="{4B8D0DED-1864-DE4D-8EAA-ED31AD29D025}"/>
   </bookViews>
   <sheets>
     <sheet name="Q1" sheetId="1" r:id="rId1"/>
@@ -1949,14 +1949,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -15541,6 +15541,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
